--- a/Dataset/Alphabets-Dataset/second-draft.xlsx
+++ b/Dataset/Alphabets-Dataset/second-draft.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="515">
   <si>
     <t>Nastaliq</t>
   </si>
@@ -1080,32 +1080,6 @@
     <t>غئیِنٚ</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>ghayeiń  (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>ġayiṅ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
     <t>graps</t>
   </si>
   <si>
@@ -1137,50 +1111,6 @@
   </si>
   <si>
     <t>/q/</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">قرقَمُش </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>قرْقمُش</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>qarqamosh  (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>qarʰqamuś</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>)</t>
-    </r>
   </si>
   <si>
     <t>hen</t>
@@ -1371,32 +1301,6 @@
     <t>نَروࣷ</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>naru (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>náro</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
     <t>shaft</t>
   </si>
   <si>
@@ -1572,69 +1476,6 @@
     <t>یٹھل</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>yatal/iathal (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>yaṭhall</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">fat-tailed sheep </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>(ewe of pamir argali
-)   male is Kaaro</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">منڈھا </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> ایشائی  جنگلی  بھیڑ جس کا تعلق ارگلی  ذات سے ہے</t>
-    </r>
-  </si>
-  <si>
     <t>یࣷ</t>
   </si>
   <si>
@@ -2159,6 +2000,133 @@
         <rFont val="Calibri"/>
       </rPr>
       <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ghayeiń  (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ġayiṅ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">قرقَمُش </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>قرْقمُش</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>qarqamosh  (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>qarʰqamuś</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>naru (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>náro</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>[w]</t>
+  </si>
+  <si>
+    <r>
+      <t>yatal/iathal (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>yaṭhall</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">fat-tailed sheep </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>(ewe of pamir argali
+)   male is Kaaro</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">منڈھا </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> ایشائی  جنگلی  بھیڑ جس کا تعلق ارگلی  ذات سے ہے</t>
     </r>
   </si>
 </sst>
@@ -2402,7 +2370,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2508,6 +2476,9 @@
     </xf>
     <xf numFmtId="0" fontId="28" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3699,7 +3670,7 @@
         <v>172</v>
       </c>
       <c r="I21" s="29" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="J21" s="8" t="s">
         <v>173</v>
@@ -3794,7 +3765,7 @@
         <v>186</v>
       </c>
       <c r="H23" s="29" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="I23" s="8" t="s">
         <v>187</v>
@@ -3843,7 +3814,7 @@
         <v>193</v>
       </c>
       <c r="H24" s="29" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="I24" s="8" t="s">
         <v>194</v>
@@ -4183,13 +4154,13 @@
         <v>237</v>
       </c>
       <c r="H32" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="I32" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="I32" s="8" t="s">
+      <c r="J32" s="8" t="s">
         <v>239</v>
-      </c>
-      <c r="J32" s="8" t="s">
-        <v>240</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
@@ -4211,22 +4182,22 @@
     </row>
     <row r="33" spans="1:27" ht="14.25" customHeight="1">
       <c r="A33" s="34" t="s">
+        <v>240</v>
+      </c>
+      <c r="B33" s="33" t="s">
         <v>241</v>
       </c>
-      <c r="B33" s="33" t="s">
+      <c r="C33" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="D33" s="36" t="s">
         <v>243</v>
-      </c>
-      <c r="D33" s="36" t="s">
-        <v>244</v>
       </c>
       <c r="E33" s="8">
         <v>641</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G33" s="8"/>
       <c r="H33" s="8"/>
@@ -4252,32 +4223,32 @@
     </row>
     <row r="34" spans="1:27" ht="14.25" customHeight="1">
       <c r="A34" s="33" t="s">
+        <v>245</v>
+      </c>
+      <c r="B34" s="33" t="s">
         <v>246</v>
       </c>
-      <c r="B34" s="33" t="s">
+      <c r="C34" s="8" t="s">
         <v>247</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>248</v>
       </c>
       <c r="D34" s="36"/>
       <c r="E34" s="8">
         <v>642</v>
       </c>
       <c r="F34" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>508</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>509</v>
+      </c>
+      <c r="I34" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="G34" s="8" t="s">
+      <c r="J34" s="8" t="s">
         <v>250</v>
-      </c>
-      <c r="H34" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="I34" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="J34" s="8" t="s">
-        <v>253</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
@@ -4299,32 +4270,32 @@
     </row>
     <row r="35" spans="1:27" ht="14.25" customHeight="1">
       <c r="A35" s="33" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B35" s="33" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D35" s="36"/>
       <c r="E35" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="H35" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="F35" s="8" t="s">
+      <c r="I35" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="G35" s="8" t="s">
+      <c r="J35" s="8" t="s">
         <v>259</v>
-      </c>
-      <c r="H35" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="I35" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="J35" s="8" t="s">
-        <v>262</v>
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
@@ -4346,32 +4317,32 @@
     </row>
     <row r="36" spans="1:27" ht="14.25" customHeight="1">
       <c r="A36" s="33" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B36" s="33" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D36" s="36"/>
       <c r="E36" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="H36" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="F36" s="8" t="s">
+      <c r="I36" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="G36" s="8" t="s">
+      <c r="J36" s="8" t="s">
         <v>268</v>
-      </c>
-      <c r="H36" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="I36" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="J36" s="8" t="s">
-        <v>271</v>
       </c>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
@@ -4393,32 +4364,32 @@
     </row>
     <row r="37" spans="1:27" ht="14.25" customHeight="1">
       <c r="A37" s="33" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B37" s="33" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D37" s="36"/>
       <c r="E37" s="8">
         <v>644</v>
       </c>
       <c r="F37" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="I37" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="G37" s="8" t="s">
+      <c r="J37" s="8" t="s">
         <v>276</v>
-      </c>
-      <c r="H37" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="I37" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="J37" s="8" t="s">
-        <v>279</v>
       </c>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
@@ -4440,32 +4411,32 @@
     </row>
     <row r="38" spans="1:27" ht="14.25" customHeight="1">
       <c r="A38" s="33" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B38" s="33" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D38" s="36"/>
       <c r="E38" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="H38" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="F38" s="8" t="s">
+      <c r="I38" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="G38" s="8" t="s">
+      <c r="J38" s="8" t="s">
         <v>284</v>
-      </c>
-      <c r="H38" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="I38" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="J38" s="8" t="s">
-        <v>287</v>
       </c>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
@@ -4487,22 +4458,22 @@
     </row>
     <row r="39" spans="1:27" ht="14.25" customHeight="1">
       <c r="A39" s="33" t="s">
+        <v>285</v>
+      </c>
+      <c r="B39" s="33" t="s">
+        <v>286</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="D39" s="36" t="s">
+        <v>287</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="F39" s="8" t="s">
         <v>288</v>
-      </c>
-      <c r="B39" s="33" t="s">
-        <v>289</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="D39" s="36" t="s">
-        <v>290</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>291</v>
       </c>
       <c r="G39" s="8"/>
       <c r="H39" s="8"/>
@@ -4528,32 +4499,32 @@
     </row>
     <row r="40" spans="1:27" ht="14.25" customHeight="1">
       <c r="A40" s="33" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B40" s="33" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D40" s="36"/>
       <c r="E40" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="H40" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="F40" s="8" t="s">
+      <c r="I40" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="G40" s="8" t="s">
+      <c r="J40" s="8" t="s">
         <v>297</v>
-      </c>
-      <c r="H40" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="I40" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="J40" s="8" t="s">
-        <v>300</v>
       </c>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
@@ -4575,32 +4546,32 @@
     </row>
     <row r="41" spans="1:27" ht="14.25" customHeight="1">
       <c r="A41" s="33" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B41" s="33" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D41" s="36"/>
       <c r="E41" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="H41" s="8" t="s">
+        <v>510</v>
+      </c>
+      <c r="I41" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="F41" s="8" t="s">
+      <c r="J41" s="10" t="s">
         <v>305</v>
-      </c>
-      <c r="G41" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="H41" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="I41" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="J41" s="10" t="s">
-        <v>309</v>
       </c>
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
@@ -4622,34 +4593,34 @@
     </row>
     <row r="42" spans="1:27" ht="14.25" customHeight="1">
       <c r="A42" s="33" t="s">
+        <v>306</v>
+      </c>
+      <c r="B42" s="33" t="s">
+        <v>307</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="D42" s="36" t="s">
+        <v>308</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="G42" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="B42" s="33" t="s">
+      <c r="H42" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="C42" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="D42" s="36" t="s">
+      <c r="I42" s="8" t="s">
         <v>312</v>
       </c>
-      <c r="E42" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="F42" s="8" t="s">
+      <c r="J42" s="8" t="s">
         <v>313</v>
-      </c>
-      <c r="G42" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="H42" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="I42" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="J42" s="8" t="s">
-        <v>317</v>
       </c>
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
@@ -4671,34 +4642,34 @@
     </row>
     <row r="43" spans="1:27" ht="14.25" customHeight="1">
       <c r="A43" s="33" t="s">
+        <v>314</v>
+      </c>
+      <c r="B43" s="33" t="s">
+        <v>315</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="D43" s="36" t="s">
+        <v>317</v>
+      </c>
+      <c r="E43" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="B43" s="33" t="s">
-        <v>319</v>
-      </c>
-      <c r="C43" s="8" t="s">
+      <c r="F43" s="8" t="s">
+        <v>511</v>
+      </c>
+      <c r="G43" s="8" t="s">
         <v>320</v>
       </c>
-      <c r="D43" s="36" t="s">
+      <c r="H43" s="8" t="s">
         <v>321</v>
       </c>
-      <c r="E43" s="8" t="s">
+      <c r="I43" s="8" t="s">
         <v>322</v>
       </c>
-      <c r="F43" s="8" t="s">
+      <c r="J43" s="8" t="s">
         <v>323</v>
-      </c>
-      <c r="G43" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="H43" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="I43" s="8" t="s">
-        <v>326</v>
-      </c>
-      <c r="J43" s="8" t="s">
-        <v>327</v>
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
@@ -4720,22 +4691,22 @@
     </row>
     <row r="44" spans="1:27" ht="14.25" customHeight="1">
       <c r="A44" s="33" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B44" s="33" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D44" s="36" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G44" s="8"/>
       <c r="H44" s="8"/>
@@ -4761,20 +4732,20 @@
     </row>
     <row r="45" spans="1:27" ht="14.25" customHeight="1">
       <c r="A45" s="35" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B45" s="35" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D45" s="36"/>
       <c r="E45" s="8" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G45" s="8"/>
       <c r="H45" s="8"/>
@@ -4800,34 +4771,34 @@
     </row>
     <row r="46" spans="1:27" ht="14.25" customHeight="1">
       <c r="A46" s="33" t="s">
+        <v>331</v>
+      </c>
+      <c r="B46" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="D46" s="36" t="s">
+        <v>332</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="F46" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="B46" s="33" t="s">
+      <c r="G46" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="C46" s="8" t="s">
+      <c r="H46" s="8" t="s">
         <v>337</v>
       </c>
-      <c r="D46" s="36" t="s">
-        <v>336</v>
-      </c>
-      <c r="E46" s="8" t="s">
+      <c r="I46" s="8" t="s">
         <v>338</v>
       </c>
-      <c r="F46" s="8" t="s">
+      <c r="J46" s="8" t="s">
         <v>339</v>
-      </c>
-      <c r="G46" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="H46" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="I46" s="8" t="s">
-        <v>342</v>
-      </c>
-      <c r="J46" s="8" t="s">
-        <v>343</v>
       </c>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
@@ -4849,34 +4820,34 @@
     </row>
     <row r="47" spans="1:27" ht="14.25" customHeight="1">
       <c r="A47" s="33" t="s">
+        <v>340</v>
+      </c>
+      <c r="B47" s="33" t="s">
+        <v>341</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="D47" s="36" t="s">
+        <v>343</v>
+      </c>
+      <c r="E47" s="8" t="s">
         <v>344</v>
       </c>
-      <c r="B47" s="33" t="s">
+      <c r="F47" s="8" t="s">
         <v>345</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="G47" s="8" t="s">
         <v>346</v>
       </c>
-      <c r="D47" s="36" t="s">
-        <v>347</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>348</v>
-      </c>
-      <c r="F47" s="8" t="s">
-        <v>349</v>
-      </c>
-      <c r="G47" s="8" t="s">
-        <v>350</v>
-      </c>
       <c r="H47" s="8" t="s">
-        <v>351</v>
-      </c>
-      <c r="I47" s="8" t="s">
-        <v>352</v>
+        <v>512</v>
+      </c>
+      <c r="I47" s="41" t="s">
+        <v>513</v>
       </c>
       <c r="J47" s="8" t="s">
-        <v>353</v>
+        <v>514</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
@@ -4898,34 +4869,34 @@
     </row>
     <row r="48" spans="1:27" ht="14.25" customHeight="1">
       <c r="A48" s="33" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="B48" s="33" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="D48" s="36" t="s">
         <v>228</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="J48" s="8" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
@@ -4949,11 +4920,11 @@
       <c r="A49" s="33"/>
       <c r="B49" s="33"/>
       <c r="C49" s="8" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="D49" s="36"/>
       <c r="E49" s="8" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="F49" s="8"/>
       <c r="G49" s="8"/>
@@ -4980,20 +4951,20 @@
     </row>
     <row r="50" spans="1:27" ht="14.25" customHeight="1">
       <c r="A50" s="33" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="B50" s="33" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="D50" s="36"/>
       <c r="E50" s="8" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="G50" s="8"/>
       <c r="H50" s="8"/>
@@ -5021,11 +4992,11 @@
       <c r="A51" s="33"/>
       <c r="B51" s="33"/>
       <c r="C51" s="8" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="D51" s="36"/>
       <c r="E51" s="8" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="F51" s="8"/>
       <c r="G51" s="8"/>
@@ -5052,17 +5023,17 @@
     </row>
     <row r="52" spans="1:27" ht="14.25" customHeight="1">
       <c r="A52" s="33" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="B52" s="33" t="s">
         <v>228</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="D52" s="36"/>
       <c r="E52" s="8" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>230</v>
@@ -5091,20 +5062,20 @@
     </row>
     <row r="53" spans="1:27" ht="14.25" customHeight="1">
       <c r="A53" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="B53" s="33" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="D53" s="36"/>
       <c r="E53" s="8" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="G53" s="8"/>
       <c r="H53" s="8"/>
@@ -5132,11 +5103,11 @@
       <c r="A54" s="33"/>
       <c r="B54" s="33"/>
       <c r="C54" s="8" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="D54" s="36"/>
       <c r="E54" s="8" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="F54" s="8"/>
       <c r="G54" s="8"/>
@@ -5163,20 +5134,20 @@
     </row>
     <row r="55" spans="1:27" ht="14.25" customHeight="1">
       <c r="A55" s="33" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="B55" s="33" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="D55" s="36"/>
       <c r="E55" s="8" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="G55" s="8"/>
       <c r="H55" s="8"/>
@@ -5202,20 +5173,20 @@
     </row>
     <row r="56" spans="1:27" ht="14.25" customHeight="1">
       <c r="A56" s="33" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="B56" s="33" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="D56" s="36"/>
       <c r="E56" s="8" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="G56" s="8"/>
       <c r="H56" s="8"/>
@@ -5241,20 +5212,20 @@
     </row>
     <row r="57" spans="1:27" ht="14.25" customHeight="1">
       <c r="A57" s="33" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="B57" s="33" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="D57" s="36"/>
       <c r="E57" s="8" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="G57" s="8"/>
       <c r="H57" s="8"/>
@@ -32675,16 +32646,16 @@
         <v>7</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="L1" s="13" t="s">
         <v>8</v>
@@ -32701,7 +32672,7 @@
         <v>11</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="E2" s="16" t="s">
         <v>12</v>
@@ -32713,13 +32684,13 @@
         <v>14</v>
       </c>
       <c r="H2" s="16" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="I2" s="16" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="J2" s="16" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="K2" s="16" t="s">
         <v>15</v>
@@ -32736,34 +32707,34 @@
         <v>20</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="E3" s="16" t="s">
         <v>21</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="I3" s="16" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="J3" s="16" t="s">
+        <v>387</v>
+      </c>
+      <c r="K3" s="16" t="s">
         <v>394</v>
       </c>
-      <c r="K3" s="16" t="s">
-        <v>401</v>
-      </c>
       <c r="L3" s="16" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -32777,31 +32748,31 @@
         <v>19</v>
       </c>
       <c r="D4" s="17" t="s">
+        <v>396</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>398</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>399</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>400</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>401</v>
+      </c>
+      <c r="J4" s="16" t="s">
+        <v>402</v>
+      </c>
+      <c r="K4" s="16" t="s">
         <v>403</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="L4" s="16" t="s">
         <v>404</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>405</v>
-      </c>
-      <c r="G4" s="16" t="s">
-        <v>406</v>
-      </c>
-      <c r="H4" s="16" t="s">
-        <v>407</v>
-      </c>
-      <c r="I4" s="16" t="s">
-        <v>408</v>
-      </c>
-      <c r="J4" s="16" t="s">
-        <v>409</v>
-      </c>
-      <c r="K4" s="16" t="s">
-        <v>410</v>
-      </c>
-      <c r="L4" s="16" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -32815,7 +32786,7 @@
         <v>38</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>39</v>
@@ -32824,16 +32795,16 @@
         <v>40</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="I5" s="16" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="J5" s="16" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="K5" s="16" t="s">
         <v>42</v>
@@ -32865,13 +32836,13 @@
         <v>50</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="J6" s="16" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="K6" s="16" t="s">
         <v>51</v>
@@ -32903,13 +32874,13 @@
         <v>59</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="J7" s="16" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="K7" s="16" t="s">
         <v>60</v>
@@ -32938,16 +32909,16 @@
         <v>67</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="J8" s="16" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="K8" s="16" t="s">
         <v>69</v>
@@ -32976,16 +32947,16 @@
         <v>81</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="J9" s="16" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="K9" s="16" t="s">
         <v>83</v>
@@ -33002,28 +32973,28 @@
         <v>88</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="F10" s="16" t="s">
         <v>91</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="J10" s="16" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="K10" s="16" t="s">
         <v>93</v>
@@ -33040,34 +33011,34 @@
         <v>103</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="F11" s="16" t="s">
         <v>106</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="J11" s="16" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="L11" s="20" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -33078,28 +33049,28 @@
         <v>113</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="F12" s="16" t="s">
         <v>116</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="I12" s="16" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="J12" s="16" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="K12" s="16" t="s">
         <v>118</v>
@@ -33131,13 +33102,13 @@
         <v>126</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="I13" s="16" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="J13" s="16" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>127</v>
@@ -33166,16 +33137,16 @@
         <v>134</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="J14" s="16" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>136</v>
@@ -33192,28 +33163,28 @@
         <v>146</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="F15" s="16" t="s">
         <v>149</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="K15" s="16" t="s">
         <v>151</v>
@@ -33242,16 +33213,16 @@
         <v>158</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="J16" s="16" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="K16" s="16" t="s">
         <v>160</v>
@@ -33277,25 +33248,25 @@
         <v>165</v>
       </c>
       <c r="F17" s="16" t="s">
+        <v>494</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="H17" s="16" t="s">
+        <v>500</v>
+      </c>
+      <c r="I17" s="16" t="s">
         <v>501</v>
       </c>
-      <c r="G17" s="16" t="s">
-        <v>506</v>
-      </c>
-      <c r="H17" s="16" t="s">
-        <v>507</v>
-      </c>
-      <c r="I17" s="16" t="s">
-        <v>508</v>
-      </c>
       <c r="J17" s="16" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -33318,13 +33289,13 @@
         <v>171</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="H18" s="16"/>
       <c r="I18" s="16"/>
       <c r="J18" s="16"/>
       <c r="K18" s="16" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="L18" s="16" t="s">
         <v>173</v>
@@ -33356,7 +33327,7 @@
       <c r="I19" s="16"/>
       <c r="J19" s="16"/>
       <c r="K19" s="16" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="L19" s="16" t="s">
         <v>180</v>
@@ -33382,7 +33353,7 @@
         <v>186</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="H20" s="16"/>
       <c r="I20" s="16"/>
@@ -33411,10 +33382,10 @@
         <v>75</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="H21" s="16"/>
       <c r="I21" s="16"/>
@@ -33446,7 +33417,7 @@
         <v>201</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="H22" s="16"/>
       <c r="I22" s="16"/>
@@ -33478,7 +33449,7 @@
         <v>210</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="H23" s="16"/>
       <c r="I23" s="16"/>
@@ -33498,10 +33469,10 @@
         <v>234</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="E24" s="16" t="s">
         <v>236</v>
@@ -33510,39 +33481,39 @@
         <v>237</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="H24" s="16"/>
       <c r="I24" s="16"/>
       <c r="J24" s="16"/>
       <c r="K24" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="L24" s="16" t="s">
         <v>239</v>
-      </c>
-      <c r="L24" s="16" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="B25" s="19" t="s">
         <v>241</v>
       </c>
-      <c r="B25" s="19" t="s">
+      <c r="C25" s="16" t="s">
         <v>242</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>243</v>
       </c>
       <c r="D25" s="16">
         <v>641</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="H25" s="16"/>
       <c r="I25" s="16"/>
@@ -33552,179 +33523,179 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="B26" s="19" t="s">
         <v>246</v>
       </c>
-      <c r="B26" s="19" t="s">
+      <c r="C26" s="16" t="s">
         <v>247</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>248</v>
       </c>
       <c r="D26" s="16">
         <v>642</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="H26" s="16"/>
       <c r="I26" s="16"/>
       <c r="J26" s="16"/>
       <c r="K26" s="16" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="D27" s="16" t="s">
         <v>254</v>
       </c>
-      <c r="B27" s="19" t="s">
+      <c r="E27" s="16" t="s">
         <v>255</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="F27" s="16" t="s">
         <v>256</v>
       </c>
-      <c r="D27" s="16" t="s">
+      <c r="G27" s="16" t="s">
         <v>257</v>
-      </c>
-      <c r="E27" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="F27" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="G27" s="16" t="s">
-        <v>260</v>
       </c>
       <c r="H27" s="16"/>
       <c r="I27" s="16"/>
       <c r="J27" s="16"/>
       <c r="K27" s="16" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="L27" s="16" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="D28" s="16" t="s">
         <v>263</v>
       </c>
-      <c r="B28" s="19" t="s">
+      <c r="E28" s="16" t="s">
         <v>264</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="F28" s="16" t="s">
         <v>265</v>
       </c>
-      <c r="D28" s="16" t="s">
-        <v>266</v>
-      </c>
-      <c r="E28" s="16" t="s">
-        <v>267</v>
-      </c>
-      <c r="F28" s="16" t="s">
-        <v>268</v>
-      </c>
       <c r="G28" s="16" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="H28" s="16"/>
       <c r="I28" s="16"/>
       <c r="J28" s="16"/>
       <c r="K28" s="16" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="L28" s="16" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="14" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D29" s="16">
         <v>644</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H29" s="16"/>
       <c r="I29" s="16"/>
       <c r="J29" s="16"/>
       <c r="K29" s="16" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="L29" s="16" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>279</v>
+      </c>
+      <c r="E30" s="16" t="s">
         <v>280</v>
       </c>
-      <c r="B30" s="19" t="s">
+      <c r="F30" s="16" t="s">
         <v>281</v>
       </c>
-      <c r="C30" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="D30" s="16" t="s">
+      <c r="G30" s="16" t="s">
         <v>282</v>
-      </c>
-      <c r="E30" s="16" t="s">
-        <v>283</v>
-      </c>
-      <c r="F30" s="16" t="s">
-        <v>284</v>
-      </c>
-      <c r="G30" s="16" t="s">
-        <v>285</v>
       </c>
       <c r="H30" s="16"/>
       <c r="I30" s="16"/>
       <c r="J30" s="16"/>
       <c r="K30" s="16" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="L30" s="16" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>279</v>
+      </c>
+      <c r="E31" s="16" t="s">
         <v>288</v>
-      </c>
-      <c r="B31" s="19" t="s">
-        <v>289</v>
-      </c>
-      <c r="C31" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="D31" s="16" t="s">
-        <v>282</v>
-      </c>
-      <c r="E31" s="16" t="s">
-        <v>291</v>
       </c>
       <c r="F31" s="16"/>
       <c r="G31" s="16"/>
@@ -33736,147 +33707,147 @@
     </row>
     <row r="32" spans="1:12">
       <c r="A32" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="D32" s="16" t="s">
         <v>292</v>
       </c>
-      <c r="B32" s="19" t="s">
+      <c r="E32" s="16" t="s">
         <v>293</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="F32" s="16" t="s">
         <v>294</v>
       </c>
-      <c r="D32" s="16" t="s">
+      <c r="G32" s="16" t="s">
         <v>295</v>
-      </c>
-      <c r="E32" s="16" t="s">
-        <v>296</v>
-      </c>
-      <c r="F32" s="16" t="s">
-        <v>297</v>
-      </c>
-      <c r="G32" s="16" t="s">
-        <v>298</v>
       </c>
       <c r="H32" s="16"/>
       <c r="I32" s="16"/>
       <c r="J32" s="16"/>
       <c r="K32" s="16" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="L32" s="16" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="D33" s="16" t="s">
         <v>301</v>
       </c>
-      <c r="B33" s="19" t="s">
+      <c r="E33" s="16" t="s">
         <v>302</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="F33" s="16" t="s">
         <v>303</v>
       </c>
-      <c r="D33" s="16" t="s">
-        <v>304</v>
-      </c>
-      <c r="E33" s="16" t="s">
-        <v>305</v>
-      </c>
-      <c r="F33" s="16" t="s">
-        <v>306</v>
-      </c>
       <c r="G33" s="16" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="H33" s="16"/>
       <c r="I33" s="16"/>
       <c r="J33" s="16"/>
       <c r="K33" s="16" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="L33" s="20" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>307</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>309</v>
+      </c>
+      <c r="F34" s="16" t="s">
         <v>310</v>
       </c>
-      <c r="B34" s="19" t="s">
-        <v>311</v>
-      </c>
-      <c r="C34" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="D34" s="16" t="s">
-        <v>304</v>
-      </c>
-      <c r="E34" s="16" t="s">
-        <v>313</v>
-      </c>
-      <c r="F34" s="16" t="s">
-        <v>314</v>
-      </c>
       <c r="G34" s="16" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="H34" s="16"/>
       <c r="I34" s="16"/>
       <c r="J34" s="16"/>
       <c r="K34" s="16" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="L34" s="16" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="B35" s="19" t="s">
+        <v>315</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="D35" s="16" t="s">
         <v>318</v>
       </c>
-      <c r="B35" s="19" t="s">
+      <c r="E35" s="16" t="s">
         <v>319</v>
       </c>
-      <c r="C35" s="16" t="s">
+      <c r="F35" s="16" t="s">
         <v>320</v>
       </c>
-      <c r="D35" s="16" t="s">
-        <v>322</v>
-      </c>
-      <c r="E35" s="16" t="s">
-        <v>323</v>
-      </c>
-      <c r="F35" s="16" t="s">
-        <v>324</v>
-      </c>
       <c r="G35" s="16" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="H35" s="16"/>
       <c r="I35" s="16"/>
       <c r="J35" s="16"/>
       <c r="K35" s="16" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="L35" s="16" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" s="14" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F36" s="16"/>
       <c r="G36" s="16"/>
@@ -33888,19 +33859,19 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" s="21" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B37" s="22" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="F37" s="16"/>
       <c r="G37" s="16"/>
@@ -33912,108 +33883,108 @@
     </row>
     <row r="38" spans="1:12">
       <c r="A38" s="14" t="s">
+        <v>331</v>
+      </c>
+      <c r="B38" s="19" t="s">
+        <v>332</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>333</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>334</v>
+      </c>
+      <c r="E38" s="16" t="s">
         <v>335</v>
       </c>
-      <c r="B38" s="19" t="s">
+      <c r="F38" s="16" t="s">
         <v>336</v>
       </c>
-      <c r="C38" s="16" t="s">
-        <v>337</v>
-      </c>
-      <c r="D38" s="16" t="s">
-        <v>338</v>
-      </c>
-      <c r="E38" s="16" t="s">
-        <v>339</v>
-      </c>
-      <c r="F38" s="16" t="s">
-        <v>340</v>
-      </c>
       <c r="G38" s="16" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="H38" s="16"/>
       <c r="I38" s="16"/>
       <c r="J38" s="16"/>
       <c r="K38" s="16" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="L38" s="16" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="B39" s="19" t="s">
+        <v>341</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>342</v>
+      </c>
+      <c r="D39" s="16" t="s">
         <v>344</v>
       </c>
-      <c r="B39" s="19" t="s">
+      <c r="E39" s="16" t="s">
         <v>345</v>
       </c>
-      <c r="C39" s="16" t="s">
+      <c r="F39" s="16" t="s">
         <v>346</v>
       </c>
-      <c r="D39" s="16" t="s">
-        <v>348</v>
-      </c>
-      <c r="E39" s="16" t="s">
-        <v>349</v>
-      </c>
-      <c r="F39" s="16" t="s">
-        <v>350</v>
-      </c>
       <c r="G39" s="16" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="H39" s="16"/>
       <c r="I39" s="16"/>
       <c r="J39" s="16"/>
       <c r="K39" s="16" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="L39" s="16" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" s="14" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="H40" s="16"/>
       <c r="I40" s="16"/>
       <c r="J40" s="16"/>
       <c r="K40" s="16" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="L40" s="16" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" s="16"/>
       <c r="B41" s="16"/>
       <c r="C41" s="16" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="E41" s="16"/>
       <c r="F41" s="16"/>
@@ -34026,19 +33997,19 @@
     </row>
     <row r="42" spans="1:12">
       <c r="A42" s="14" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="F42" s="16"/>
       <c r="G42" s="16"/>
@@ -34052,10 +34023,10 @@
       <c r="A43" s="16"/>
       <c r="B43" s="16"/>
       <c r="C43" s="16" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="E43" s="16"/>
       <c r="F43" s="16"/>
@@ -34068,16 +34039,16 @@
     </row>
     <row r="44" spans="1:12">
       <c r="A44" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="B44" s="19" t="s">
         <v>228</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="E44" s="16" t="s">
         <v>230</v>
@@ -34092,19 +34063,19 @@
     </row>
     <row r="45" spans="1:12">
       <c r="A45" s="14" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="F45" s="16"/>
       <c r="G45" s="16"/>
@@ -34118,10 +34089,10 @@
       <c r="A46" s="16"/>
       <c r="B46" s="16"/>
       <c r="C46" s="16" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="E46" s="16"/>
       <c r="F46" s="16"/>
@@ -34134,19 +34105,19 @@
     </row>
     <row r="47" spans="1:12">
       <c r="A47" s="14" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="B47" s="19" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="C47" s="16" t="s">
+        <v>363</v>
+      </c>
+      <c r="D47" s="16" t="s">
+        <v>364</v>
+      </c>
+      <c r="E47" s="16" t="s">
         <v>370</v>
-      </c>
-      <c r="D47" s="16" t="s">
-        <v>371</v>
-      </c>
-      <c r="E47" s="16" t="s">
-        <v>377</v>
       </c>
       <c r="F47" s="16"/>
       <c r="G47" s="16"/>
@@ -34158,19 +34129,19 @@
     </row>
     <row r="48" spans="1:12">
       <c r="A48" s="14" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="F48" s="16"/>
       <c r="G48" s="16"/>
@@ -34182,19 +34153,19 @@
     </row>
     <row r="49" spans="1:12">
       <c r="A49" s="14" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="E49" s="16" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="F49" s="16"/>
       <c r="G49" s="16"/>
@@ -34224,86 +34195,86 @@
   <sheetData>
     <row r="1" spans="1:4" s="23" customFormat="1" ht="22.8" customHeight="1">
       <c r="A1" s="23" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="B1" s="23" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="C1" s="23" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="D1" s="23" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="24" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="C2" s="24"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="24" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="C3" s="24"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="26" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="24" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="24" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="C10" s="24" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="24" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="B11" s="24"/>
     </row>
